--- a/output/北塩原村_レビュー対応と素案修正方針.xlsx
+++ b/output/北塩原村_レビュー対応と素案修正方針.xlsx
@@ -583,7 +583,7 @@
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>4. ただし差し替えは、どちらの系列を計画値とするかを村に確認したうえで行います（M-19）。村の公表値は自立支援協議会に報告済みの数値であり、当方が勝手に別の系列へ移すと協議会への説明が通らなくなるためです。</t>
+          <t>4. ただし差し替えは、どちらの系列を計画値とするかを村に確認したうえで行います（Ｍ-19）。村の公表値は自立支援協議会に報告済みの数値であり、当方が勝手に別の系列へ移すと協議会への説明が通らなくなるためです。</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>第5章7の考え方欄に、放課後児童クラブ・小中学校・特別支援学校の受入状況を勘案する旨を書く。村への照会（M-11）の回答を待って数値を入れる</t>
+          <t>第5章7の考え方欄に、放課後児童クラブ・小中学校・特別支援学校の受入状況を勘案する旨を書く。村への照会（Ｍ-11）の回答を待って数値を入れる</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>計画本文には出さない。村への照会（M-18）として台帳の様式を示し、受領後に第2次算定の基礎とする。素案 第5章1には「個別の積上げは村の個別データを受領した後の第2次算定で行う」と既に書いてあり、その入力がこの台帳である旨を補う</t>
+          <t>計画本文には出さない。村への照会（Ｍ-18）として台帳の様式を示し、受領後に第2次算定の基礎とする。素案 第5章1には「個別の積上げは村の個別データを受領した後の第2次算定で行う」と既に書いてあり、その入力がこの台帳である旨を補う</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>村照会（M-18）・第5章1</t>
+          <t>村照会（Ｍ-18）・第5章1</t>
         </is>
       </c>
     </row>
@@ -2673,7 +2673,7 @@
     <row r="33" ht="58" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>村の実利用者数は月平均（小数を含む）であり、当方の第1次概算は年間請求件数を12で割らずにサービスごとの考え方で人数に置いたものである。したがって差は誤りではなく系列の違いだが、計画値として協議会に報告するのは村の系列であるため、基礎を村の公表値に置き換えるのが筋である。どちらを計画値とするかを村に確認する（M-19）。</t>
+          <t>村の実利用者数は月平均（小数を含む）であり、当方の第1次概算は年間請求件数を12で割らずにサービスごとの考え方で人数に置いたものである。したがって差は誤りではなく系列の違いだが、計画値として協議会に報告するのは村の系列であるため、基礎を村の公表値に置き換えるのが筋である。どちらを計画値とするかを村に確認する（Ｍ-19）。</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>次回。どちらの系列を計画値とするかを村に1点確認したうえで差し替える（M-19）</t>
+          <t>次回。どちらの系列を計画値とするかを村に1点確認したうえで差し替える（Ｍ-19）</t>
         </is>
       </c>
     </row>
@@ -3761,14 +3761,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>村への確認事項（M-18・M-19）</t>
+          <t>村への確認事項（Ｍ-18・Ｍ-19）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>既存のM-1〜M-17に続けて番号を付した。M-19は見込量の基礎の置き換えに必要なため最優先とする。</t>
+          <t>既存のＭ-1〜Ｍ-17に続けて番号を付した。Ｍ-19は見込量の基礎の置き換えに必要なため最優先とする。</t>
         </is>
       </c>
     </row>
@@ -3797,7 +3797,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>M-19</t>
+          <t>Ｍ-19</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -3819,7 +3819,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>M-18</t>
+          <t>Ｍ-18</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -3841,7 +3841,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>M-20</t>
+          <t>Ｍ-20</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -3863,7 +3863,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>M-21</t>
+          <t>Ｍ-21</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
